--- a/오류 케이스.xlsx
+++ b/오류 케이스.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>입력 파일</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -98,6 +98,18 @@
   </si>
   <si>
     <t>위계가 있으니 일단 에러가 뜬 이상 에러를 젤 최상단으로.../</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전입생 명단에 신입생 중복</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미 명부에 존재하는 전입생 (학년, 반, 이름 동일)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선생님 관리용 아이디 신청이 한 건도 없음</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -545,7 +557,7 @@
   <dimension ref="A1:E68"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.125" customWidth="1"/>
+    <col min="1" max="1" width="43.125" customWidth="1"/>
     <col min="2" max="2" width="27.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -628,6 +640,21 @@
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="5:5" x14ac:dyDescent="0.3">

--- a/오류 케이스.xlsx
+++ b/오류 케이스.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>입력 파일</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -110,6 +110,18 @@
   </si>
   <si>
     <t>선생님 관리용 아이디 신청이 한 건도 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>반 이름이 미편성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>반 열에 유치원, 학년 열에 유치원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학년 열에 유치원, 반 열에 민들레, 진달래 등</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -657,6 +669,21 @@
         <v>22</v>
       </c>
     </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="52" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E52" t="s">
         <v>17</v>
